--- a/Feuilles/Metamorphose.xlsx
+++ b/Feuilles/Metamorphose.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E4BD37-9393-AC43-BCFC-E38F1396E60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A52759-AC13-7B4F-B09A-597144717303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2680" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>MES</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>Transition 3</t>
+  </si>
+  <si>
+    <t>LOOP</t>
   </si>
 </sst>
 </file>
@@ -467,10 +470,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,8 +486,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -498,7 +504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -509,7 +515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -520,7 +526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -531,7 +537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -542,7 +548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -553,7 +559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -564,7 +570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -575,7 +581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -589,7 +595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -600,7 +606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -611,7 +617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -622,7 +628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -633,7 +639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -644,7 +650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Feuilles/Metamorphose.xlsx
+++ b/Feuilles/Metamorphose.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A52759-AC13-7B4F-B09A-597144717303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808F7531-D0C6-0449-8882-C38B61504C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2680" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -685,8 +685,11 @@
       <c r="D18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -697,7 +700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -708,7 +711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -719,7 +722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -730,7 +733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -741,7 +744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -754,8 +757,11 @@
       <c r="D24" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -766,7 +772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -777,7 +783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -788,7 +794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -802,7 +808,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -813,7 +819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -824,7 +830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -835,7 +841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -846,7 +852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -857,7 +863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -868,7 +874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -879,7 +885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -892,8 +898,11 @@
       <c r="D36" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -904,7 +913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -915,7 +924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -926,7 +935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -937,7 +946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -948,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -961,8 +970,11 @@
       <c r="D42" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -973,7 +985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -984,7 +996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -995,7 +1007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1009,7 +1021,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1020,7 +1032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1031,7 +1043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1042,7 +1054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1053,7 +1065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1064,7 +1076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1075,7 +1087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1086,7 +1098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1099,8 +1111,11 @@
       <c r="D54" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1111,7 +1126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1122,7 +1137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1133,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1144,7 +1159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1155,7 +1170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1168,8 +1183,11 @@
       <c r="D60" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1180,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1191,7 +1209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1202,7 +1220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1213,7 +1231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1224,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1235,7 +1253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1246,7 +1264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1259,8 +1277,11 @@
       <c r="D68" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1271,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1282,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1293,7 +1314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1304,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1315,7 +1336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1328,8 +1349,11 @@
       <c r="D74" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1340,7 +1364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1351,7 +1375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1362,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1376,7 +1400,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1387,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1398,7 +1422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1409,7 +1433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1420,7 +1444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1431,7 +1455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1442,7 +1466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1453,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1466,8 +1490,11 @@
       <c r="D86" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1478,7 +1505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1489,7 +1516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1500,7 +1527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1511,7 +1538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1522,7 +1549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1532,8 +1559,11 @@
       <c r="C92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1544,7 +1574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1555,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1566,7 +1596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
